--- a/gen-sticker-docs/originals/04 – Software Architecture & Technical Design.xlsx
+++ b/gen-sticker-docs/originals/04 – Software Architecture & Technical Design.xlsx
@@ -2,21 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual System Context" sheetId="1" r:id="R552b262f47974c6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Sequence" sheetId="2" r:id="Rf5f6549019b24ce5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Pipeline" sheetId="3" r:id="R41dd1bea32a64ec5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Context" sheetId="4" r:id="R253ee0daef81483b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Flow" sheetId="5" r:id="Rbfbd1a11214b4600"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module Map" sheetId="6" r:id="R8d9ed13592cf46ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrations" sheetId="7" r:id="R3b1e56abc94241ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State &amp; Data" sheetId="8" r:id="R11e9510625994bc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture Decisions" sheetId="9" r:id="R018850c5328c4cf3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Component Responsibilities" sheetId="10" r:id="Ree912782ffad4b21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Sequence" sheetId="11" r:id="R4cff3aa2306047c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deployment Topology" sheetId="12" r:id="R4de69d70fcfa400c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Boundaries" sheetId="13" r:id="R5c25973687d241ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure Modes" sheetId="14" r:id="R5c4066a1fdac4b85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADR Register" sheetId="15" r:id="R9181c58f54ef423c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual System Context" sheetId="1" r:id="R6f67c66fee3e42ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Sequence" sheetId="2" r:id="Rd42fa60c8920499f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Pipeline" sheetId="3" r:id="R55f31ea401d14d79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Context" sheetId="4" r:id="Rd606540e6947488d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Flow" sheetId="5" r:id="Rdc67fa8057a1419e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module Map" sheetId="6" r:id="Rd32cd7e4a1e94c73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrations" sheetId="7" r:id="R69780b940aee4723"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State &amp; Data" sheetId="8" r:id="R99deff2231df4220"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture Decisions" sheetId="9" r:id="R7fcad0ac252a441f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Component Responsibilities" sheetId="10" r:id="R6e554bdf481e40cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Sequence" sheetId="11" r:id="R791e589f10e8473e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deployment Topology" sheetId="12" r:id="Rd125e9aaa5da488c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Boundaries" sheetId="13" r:id="R9d0cffb81d0845f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure Modes" sheetId="14" r:id="R23eb7ce6ac7f485e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADR Register" sheetId="15" r:id="Rd8a6c58996734ba3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Face Gate Architecture" sheetId="16" r:id="Ra523eae0bc994739"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -421,13 +422,13 @@
     <xdr:ext cx="11734800" cy="6600825"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="3b28611c-ce2e-4a66-b1e9-4166df3fbafa"/>
+        <xdr:cNvPr id="1" name="978da343-7b74-4513-a479-bc60bea5b059"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra19d125e8b1b45c2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R96675a3a4fa44f52"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -453,13 +454,13 @@
     <xdr:ext cx="11734800" cy="6600825"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="5c940cf7-f909-4a75-a817-02368e3dd761"/>
+        <xdr:cNvPr id="1" name="4ab34d2c-8f9c-49e6-b3f0-8a4a4fe113e5"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R845ab29c3ed14fb7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R1994357bf68641bc"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -485,13 +486,13 @@
     <xdr:ext cx="11734800" cy="6600825"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="93174a30-e766-4890-a93c-be8b9b36be2c"/>
+        <xdr:cNvPr id="1" name="a1498d4f-b1fc-476c-b44c-cff466aa0f2a"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R01899258e89e4d0a"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb8aed514aced42ae"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -554,6 +555,20 @@
     <x:tableColumn id="3" name="Rationale"/>
     <x:tableColumn id="4" name="Trade-off"/>
     <x:tableColumn id="5" name="Revisit when"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="GS0413Table" displayName="GS0413Table" ref="A6:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:E12"/>
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="Layer"/>
+    <x:tableColumn id="2" name="Component/data"/>
+    <x:tableColumn id="3" name="Responsibility"/>
+    <x:tableColumn id="4" name="Failure behavior"/>
+    <x:tableColumn id="5" name="Deployment"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -902,7 +917,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Component topology hiện tại và các external trust boundaries</x:v>
+        <x:v>MediaPipe CPU/WASM trên client, backend grouped pipeline không đổi</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -954,7 +969,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="16" t="str">
-        <x:v>Browser gọi React, React gọi FastAPI</x:v>
+        <x:v>Browser chứa React và FaceDetector worker</x:v>
       </x:c>
       <x:c r="B8" s="16"/>
       <x:c r="C8" s="16"/>
@@ -962,7 +977,7 @@
       <x:c r="E8" s="16"/>
       <x:c r="F8" s="16"/>
       <x:c r="I8" s="22" t="str">
-        <x:v>FastAPI điều phối grouped generator, RAM/temp, Supabase, Image API và Telegram</x:v>
+        <x:v>Vite/Vercel phục vụ model BlazeFace</x:v>
       </x:c>
       <x:c r="J8" s="22"/>
       <x:c r="K8" s="22"/>
@@ -1048,7 +1063,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="28" t="str">
-        <x:v>Component topology runtime và các external trust boundaries.</x:v>
+        <x:v>worker tải WASM từ jsDelivr</x:v>
       </x:c>
       <x:c r="B18" s="28"/>
       <x:c r="C18" s="28"/>
@@ -1056,7 +1071,7 @@
       <x:c r="E18" s="28"/>
       <x:c r="F18" s="28"/>
       <x:c r="I18" s="34" t="str">
-        <x:v>Component topology runtime và các external trust boundaries.</x:v>
+        <x:v>ảnh pass mới được gửi FastAPI, grouped generator và Image API</x:v>
       </x:c>
       <x:c r="J18" s="34"/>
       <x:c r="K18" s="34"/>
@@ -1142,7 +1157,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="43" t="str">
-        <x:v>Component topology hiện tại và các external trust boundaries
+        <x:v>MediaPipe CPU/WASM trên client, backend grouped pipeline không đổi
 Implemented  •  Inferred  •  Gap/Risk  •  Recommended</x:v>
       </x:c>
       <x:c r="B28" s="43"/>
@@ -1225,7 +1240,7 @@
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
       <x:c r="A42" s="45" t="str">
-        <x:v>Hình GS-DOC-04 — Kiến trúc runtime GenSticker. Component topology runtime và các external trust boundaries.</x:v>
+        <x:v>Hình GS-DOC-04 — Kiến trúc runtime GenSticker. Runtime topology có MediaPipe worker chạy trên CPU client, model tĩnh cùng origin và WASM tải từ CDN ghim phiên bản.</x:v>
       </x:c>
       <x:c r="B42" s="45"/>
       <x:c r="C42" s="45"/>
@@ -1243,7 +1258,7 @@
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
       <x:c r="A44" s="49" t="str">
-        <x:v>Mô tả sơ đồ: Browser gọi React, React gọi FastAPI; FastAPI điều phối grouped generator, RAM/temp, Supabase, Image API và Telegram.</x:v>
+        <x:v>Mô tả sơ đồ: Browser chứa React và FaceDetector worker; Vite/Vercel phục vụ model BlazeFace; worker tải WASM từ jsDelivr; ảnh pass mới được gửi FastAPI, grouped generator và Image API; Supabase và Telegram giữ nguyên.</x:v>
       </x:c>
       <x:c r="B44" s="49"/>
       <x:c r="C44" s="49"/>
@@ -1261,7 +1276,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="51" t="str">
-        <x:v>Nguồn: backend/app/main.py; backend/app/services/sticker_pipeline.py; backend/sticker_generation/grouped.py  •  kien_v5 @ c09e26a  •  2026-08-09</x:v>
+        <x:v>Nguồn: frontend/src/services/faceDetectionService.ts; frontend/src/workers/faceDetector.worker.ts; frontend/public/models/README.md  •  kien_v5 @ 4d23b9a  •  2026-08-10</x:v>
       </x:c>
       <x:c r="B46" s="51"/>
       <x:c r="C46" s="51"/>
@@ -1296,7 +1311,7 @@
   <x:printOptions horizontalCentered="1"/>
   <x:pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10dd857395654691"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99e4edfa7a554505"/>
 </x:worksheet>
 </file>
 
@@ -1328,7 +1343,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-04  •  kien_v5 @ c09e26a  •  2026-08-09  •  Source verified</x:v>
+        <x:v>GS-DOC-04  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Source verified</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1449,7 +1464,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a8d596a802844b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8adb90a36ba48ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1485,7 +1500,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-04  •  kien_v5 @ c09e26a  •  2026-08-09  •  Source verified</x:v>
+        <x:v>GS-DOC-04  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Source verified</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1595,7 +1610,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9668e3f91beb48a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35a18d802c944600"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1628,7 +1643,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-04  •  kien_v5 @ c09e26a  •  2026-08-09  •  Source verified</x:v>
+        <x:v>GS-DOC-04  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Source verified</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1735,7 +1750,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0593004f7f6f44e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3401077cb1c4051"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1768,7 +1783,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-04  •  kien_v5 @ c09e26a  •  2026-08-09  •  Source verified</x:v>
+        <x:v>GS-DOC-04  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Source verified</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1875,7 +1890,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ed795bb1d0f4ca3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fe6e38db4dd42de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1908,7 +1923,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-04  •  kien_v5 @ c09e26a  •  2026-08-09  •  Source verified</x:v>
+        <x:v>GS-DOC-04  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Source verified</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2015,7 +2030,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R503b3404e62040db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3c54732164f40d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2051,7 +2066,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-04  •  kien_v5 @ c09e26a  •  2026-08-09  •  Source verified</x:v>
+        <x:v>GS-DOC-04  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Source verified</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2178,7 +2193,187 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09680ab1d5cf4461"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94ec2bcee2cc4f2b"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="38" customHeight="1">
+      <x:c r="A1" s="53" t="str">
+        <x:v>04  /  Software Architecture &amp; Technical Design</x:v>
+      </x:c>
+      <x:c r="B1" s="53"/>
+      <x:c r="C1" s="53"/>
+      <x:c r="D1" s="53"/>
+      <x:c r="E1" s="53"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="56" t="str">
+        <x:v>Component, dữ liệu, dependency và failure boundary của detector browser</x:v>
+      </x:c>
+      <x:c r="B2" s="56"/>
+      <x:c r="C2" s="56"/>
+      <x:c r="D2" s="56"/>
+      <x:c r="E2" s="56"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="57" t="str">
+        <x:v>GS-DOC-04  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Source verified</x:v>
+      </x:c>
+      <x:c r="B3" s="57"/>
+      <x:c r="C3" s="57"/>
+      <x:c r="D3" s="57"/>
+      <x:c r="E3" s="57"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="58" t="str">
+        <x:v>AS-BUILT • Nội dung viết từ source hiện tại; bộ mẫu chỉ cung cấp cấu trúc trình bày.</x:v>
+      </x:c>
+      <x:c r="B4" s="58"/>
+      <x:c r="C4" s="58"/>
+      <x:c r="D4" s="58"/>
+      <x:c r="E4" s="58"/>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="64" t="str">
+        <x:v>Layer</x:v>
+      </x:c>
+      <x:c r="B6" s="64" t="str">
+        <x:v>Component/data</x:v>
+      </x:c>
+      <x:c r="C6" s="64" t="str">
+        <x:v>Responsibility</x:v>
+      </x:c>
+      <x:c r="D6" s="64" t="str">
+        <x:v>Failure behavior</x:v>
+      </x:c>
+      <x:c r="E6" s="64" t="str">
+        <x:v>Deployment</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A7" s="69" t="str">
+        <x:v>UI</x:v>
+      </x:c>
+      <x:c r="B7" s="69" t="str">
+        <x:v>ImageUploader + useImageUpload</x:v>
+      </x:c>
+      <x:c r="C7" s="69" t="str">
+        <x:v>State idle/checking/verified; copy/CTA</x:v>
+      </x:c>
+      <x:c r="D7" s="69" t="str">
+        <x:v>Reject inline; stale result ignored</x:v>
+      </x:c>
+      <x:c r="E7" s="69" t="str">
+        <x:v>Vite static</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="54" hidden="0" customHeight="1">
+      <x:c r="A8" s="70" t="str">
+        <x:v>Service</x:v>
+      </x:c>
+      <x:c r="B8" s="70" t="str">
+        <x:v>faceDetectionService</x:v>
+      </x:c>
+      <x:c r="C8" s="70" t="str">
+        <x:v>Worker singleton, request map, 45s timeout</x:v>
+      </x:c>
+      <x:c r="D8" s="70" t="str">
+        <x:v>Terminate/reset; reject pending</x:v>
+      </x:c>
+      <x:c r="E8" s="70" t="str">
+        <x:v>Browser runtime</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="54" hidden="0" customHeight="1">
+      <x:c r="A9" s="69" t="str">
+        <x:v>Worker</x:v>
+      </x:c>
+      <x:c r="B9" s="69" t="str">
+        <x:v>faceDetector.worker</x:v>
+      </x:c>
+      <x:c r="C9" s="69" t="str">
+        <x:v>MediaPipe detect on transferred ImageBitmap</x:v>
+      </x:c>
+      <x:c r="D9" s="69" t="str">
+        <x:v>Fail closed; bitmap close</x:v>
+      </x:c>
+      <x:c r="E9" s="69" t="str">
+        <x:v>Module worker chunk</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A10" s="70" t="str">
+        <x:v>Model</x:v>
+      </x:c>
+      <x:c r="B10" s="70" t="str">
+        <x:v>BlazeFace short-range TFLite</x:v>
+      </x:c>
+      <x:c r="C10" s="70" t="str">
+        <x:v>Human face detections</x:v>
+      </x:c>
+      <x:c r="D10" s="70" t="str">
+        <x:v>Missing model rejects</x:v>
+      </x:c>
+      <x:c r="E10" s="70" t="str">
+        <x:v>Same-origin public/models</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A11" s="69" t="str">
+        <x:v>WASM</x:v>
+      </x:c>
+      <x:c r="B11" s="69" t="str">
+        <x:v>MediaPipe Tasks Vision 1.0.1</x:v>
+      </x:c>
+      <x:c r="C11" s="69" t="str">
+        <x:v>CPU inference runtime</x:v>
+      </x:c>
+      <x:c r="D11" s="69" t="str">
+        <x:v>CDN/network error rejects</x:v>
+      </x:c>
+      <x:c r="E11" s="69" t="str">
+        <x:v>Pinned jsDelivr URL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A12" s="70" t="str">
+        <x:v>API</x:v>
+      </x:c>
+      <x:c r="B12" s="70" t="str">
+        <x:v>FastAPI generate</x:v>
+      </x:c>
+      <x:c r="C12" s="70" t="str">
+        <x:v>Unchanged multipart/JWT contract</x:v>
+      </x:c>
+      <x:c r="D12" s="70" t="str">
+        <x:v>No server semantic check</x:v>
+      </x:c>
+      <x:c r="E12" s="70" t="str">
+        <x:v>Separate backend</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A3:E3"/>
+    <x:mergeCell ref="A4:E4"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77f4970dc73f41df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2226,7 +2421,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>4 image requests/job: canonical + ba sheet landscape, sau đó structural QA và persistence best-effort</x:v>
+        <x:v>Preflight exact-one-face trước POST; pass mới phát sinh canonical + ba sheet</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -2278,7 +2473,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="16" t="str">
-        <x:v>Swimlane từ Browser qua FastAPI, Pipeline, Image API, Quality và Supabase</x:v>
+        <x:v>Browser gửi ImageBitmap cho Face Worker</x:v>
       </x:c>
       <x:c r="B8" s="16"/>
       <x:c r="C8" s="16"/>
@@ -2286,7 +2481,7 @@
       <x:c r="E8" s="16"/>
       <x:c r="F8" s="16"/>
       <x:c r="I8" s="22" t="str">
-        <x:v>gồm canonical, ba sheet, crop và poll kết quả</x:v>
+        <x:v>nhánh 0, nhiều mặt hoặc lỗi dừng cục bộ</x:v>
       </x:c>
       <x:c r="J8" s="22"/>
       <x:c r="K8" s="22"/>
@@ -2372,7 +2567,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="28" t="str">
-        <x:v>Sequence bốn image request, structural QA, polling và persistence best-effort.</x:v>
+        <x:v>nhánh một mặt POST FastAPI rồi tạo canonical, ba sheet, structural QA và persistence best-effort</x:v>
       </x:c>
       <x:c r="B18" s="28"/>
       <x:c r="C18" s="28"/>
@@ -2380,7 +2575,7 @@
       <x:c r="E18" s="28"/>
       <x:c r="F18" s="28"/>
       <x:c r="I18" s="34" t="str">
-        <x:v>Sequence bốn image request, structural QA, polling và persistence best-effort.</x:v>
+        <x:v>Sequence bắt đầu bằng exact-one-face preflight cục bộ; chỉ nhánh pass mới phát sinh POST và bốn image request.</x:v>
       </x:c>
       <x:c r="J18" s="34"/>
       <x:c r="K18" s="34"/>
@@ -2466,7 +2661,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="43" t="str">
-        <x:v>4 image requests/job: canonical + ba sheet landscape, sau đó structural QA và persistence best-effort
+        <x:v>Preflight exact-one-face trước POST; pass mới phát sinh canonical + ba sheet
 Implemented  •  Inferred  •  Gap/Risk  •  Recommended</x:v>
       </x:c>
       <x:c r="B28" s="43"/>
@@ -2549,7 +2744,7 @@
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
       <x:c r="A42" s="45" t="str">
-        <x:v>Hình GS-DOC-04 — Sequence tạo một bộ 20 sticker. Sequence bốn image request, structural QA, polling và persistence best-effort.</x:v>
+        <x:v>Hình GS-DOC-04 — Sequence tạo một bộ 20 sticker. Sequence bắt đầu bằng exact-one-face preflight cục bộ; chỉ nhánh pass mới phát sinh POST và bốn image request.</x:v>
       </x:c>
       <x:c r="B42" s="45"/>
       <x:c r="C42" s="45"/>
@@ -2567,7 +2762,7 @@
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
       <x:c r="A44" s="49" t="str">
-        <x:v>Mô tả sơ đồ: Swimlane từ Browser qua FastAPI, Pipeline, Image API, Quality và Supabase; gồm canonical, ba sheet, crop và poll kết quả.</x:v>
+        <x:v>Mô tả sơ đồ: Browser gửi ImageBitmap cho Face Worker; nhánh 0, nhiều mặt hoặc lỗi dừng cục bộ; nhánh một mặt POST FastAPI rồi tạo canonical, ba sheet, structural QA và persistence best-effort.</x:v>
       </x:c>
       <x:c r="B44" s="49"/>
       <x:c r="C44" s="49"/>
@@ -2585,7 +2780,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="51" t="str">
-        <x:v>Nguồn: backend/sticker_generation/grouped.py; backend/sticker_generation/providers/openai_image.py; backend/app/services/sticker_pipeline.py  •  kien_v5 @ c09e26a  •  2026-08-09</x:v>
+        <x:v>Nguồn: frontend/src/services/faceDetectionService.ts; frontend/src/workers/faceDetector.worker.ts; backend/sticker_generation/grouped.py  •  kien_v5 @ 4d23b9a  •  2026-08-10</x:v>
       </x:c>
       <x:c r="B46" s="51"/>
       <x:c r="C46" s="51"/>
@@ -2620,7 +2815,7 @@
   <x:printOptions horizontalCentered="1"/>
   <x:pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdca934876c546ed"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R553bede6bac04c5c"/>
 </x:worksheet>
 </file>
 
@@ -3026,7 +3221,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="51" t="str">
-        <x:v>Nguồn: backend/app/services/sticker_pipeline.py; backend/sticker_generation/identity.py; backend/sticker_generation/postprocess.py  •  kien_v5 @ c09e26a  •  2026-08-09</x:v>
+        <x:v>Nguồn: backend/app/services/sticker_pipeline.py; backend/sticker_generation/identity.py; backend/sticker_generation/postprocess.py  •  kien_v5 @ 4d23b9a  •  2026-08-10</x:v>
       </x:c>
       <x:c r="B46" s="51"/>
       <x:c r="C46" s="51"/>
@@ -3061,7 +3256,7 @@
   <x:printOptions horizontalCentered="1"/>
   <x:pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd66f9f2596b04440"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd43ecc4aa49465d"/>
 </x:worksheet>
 </file>
 
@@ -3096,7 +3291,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-04  •  kien_v5 @ c09e26a  •  2026-08-09  •  Source verified</x:v>
+        <x:v>GS-DOC-04  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Source verified</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3240,7 +3435,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ef96743d12346af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8a28477cc174864"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3276,7 +3471,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-04  •  kien_v5 @ c09e26a  •  2026-08-09  •  Source verified</x:v>
+        <x:v>GS-DOC-04  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Source verified</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3488,7 +3683,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01dc7fa8d7004ace"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1100b98168d3468e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3521,7 +3716,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-04  •  kien_v5 @ c09e26a  •  2026-08-09  •  Source verified</x:v>
+        <x:v>GS-DOC-04  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Source verified</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3670,7 +3865,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b5916ad6c07437f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f303b52a6bb4e3a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3706,7 +3901,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-04  •  kien_v5 @ c09e26a  •  2026-08-09  •  Source verified</x:v>
+        <x:v>GS-DOC-04  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Source verified</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3833,7 +4028,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R202dde67ad954c83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb902dbdb7fe449a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3869,7 +4064,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-04  •  kien_v5 @ c09e26a  •  2026-08-09  •  Source verified</x:v>
+        <x:v>GS-DOC-04  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Source verified</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -4013,7 +4208,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43ad488bacea4291"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdecfa9facb24a3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4049,7 +4244,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-04  •  kien_v5 @ c09e26a  •  2026-08-09  •  Source verified</x:v>
+        <x:v>GS-DOC-04  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Source verified</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -4176,7 +4371,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb780c12ba7d84d10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9f611c78b754f42"/>
   </x:tableParts>
 </x:worksheet>
 </file>